--- a/tiflow-core/fhir-error-codes/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Communication-DispReq.xlsx
+++ b/tiflow-core/fhir-error-codes/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Communication-DispReq.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2091" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2100" uniqueCount="402">
   <si>
     <t>Property</t>
   </si>
@@ -496,6 +496,13 @@
     <t>Meta.security</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
     <t>Communication.meta.tag</t>
   </si>
   <si>
@@ -643,10 +650,6 @@
     <t>Definiert den Typ des Rezepts. Das Codesystem enthält alle unterstützten Formulare.</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>Communication.modifierExtension</t>
   </si>
   <si>
@@ -688,6 +691,9 @@
     <t>FiveWs.identifier</t>
   </si>
   <si>
+    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
+  </si>
+  <si>
     <t>Communication.instantiatesCanonical</t>
   </si>
   <si>
@@ -701,6 +707,9 @@
     <t>The URL pointing to a FHIR-defined protocol, guideline, orderset or other definition that is adhered to in whole or in part by this Communication.</t>
   </si>
   <si>
+    <t>see [Canonical References](http://hl7.org/fhir/R4/references.html#canonical)</t>
+  </si>
+  <si>
     <t>Event.instantiatesCanonical</t>
   </si>
   <si>
@@ -742,7 +751,14 @@
     <t>This must point to some sort of a 'Request' resource, such as CarePlan, CommunicationRequest, ServiceRequest, MedicationRequest, etc.</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
     <t>Event.basedOn</t>
+  </si>
+  <si>
+    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
   </si>
   <si>
     <t>Communication.partOf</t>
@@ -758,6 +774,9 @@
     <t>Part of this action.</t>
   </si>
   <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
     <t>Event.partOf</t>
   </si>
   <si>
@@ -830,6 +849,9 @@
     <t>Event.statusReason</t>
   </si>
   <si>
+    <t>CD</t>
+  </si>
+  <si>
     <t>Communication.category</t>
   </si>
   <si>
@@ -882,6 +904,9 @@
   </si>
   <si>
     <t>A channel that was used for this communication (e.g. email, fax).</t>
+  </si>
+  <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
   </si>
   <si>
     <t>Codes for communication mediums such as phone, fax, email, in person, etc.</t>
@@ -1241,7 +1266,13 @@
     <t>Additional notes or commentary about the communication by the sender, receiver or other interested parties.</t>
   </si>
   <si>
+    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
+  </si>
+  <si>
     <t>Event.note</t>
+  </si>
+  <si>
+    <t>Act</t>
   </si>
 </sst>
 </file>
@@ -1598,7 +1629,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="43.421875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="38.5234375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="123.23828125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2922,7 +2953,7 @@
         <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>98</v>
@@ -2934,15 +2965,15 @@
         <v>76</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>76</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2968,13 +2999,13 @@
         <v>146</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3000,13 +3031,13 @@
         <v>76</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>76</v>
@@ -3024,7 +3055,7 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
@@ -3033,7 +3064,7 @@
         <v>78</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>98</v>
@@ -3045,15 +3076,15 @@
         <v>76</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>76</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3079,13 +3110,13 @@
         <v>128</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3135,7 +3166,7 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -3161,10 +3192,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3187,16 +3218,16 @@
         <v>76</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3222,13 +3253,13 @@
         <v>76</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>76</v>
@@ -3246,7 +3277,7 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -3272,14 +3303,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3298,16 +3329,16 @@
         <v>76</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3357,7 +3388,7 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3378,19 +3409,19 @@
         <v>76</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3409,16 +3440,16 @@
         <v>76</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3468,7 +3499,7 @@
         <v>76</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3489,15 +3520,15 @@
         <v>76</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3523,10 +3554,10 @@
         <v>107</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3577,7 +3608,7 @@
         <v>113</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -3603,13 +3634,13 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>76</v>
@@ -3631,13 +3662,13 @@
         <v>76</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3688,7 +3719,7 @@
         <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -3697,7 +3728,7 @@
         <v>78</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>201</v>
+        <v>76</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>115</v>
@@ -3714,10 +3745,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3743,16 +3774,16 @@
         <v>107</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N20" t="s" s="2">
         <v>110</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>76</v>
@@ -3789,19 +3820,19 @@
         <v>76</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3822,15 +3853,15 @@
         <v>76</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3853,19 +3884,19 @@
         <v>87</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>76</v>
@@ -3914,7 +3945,7 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -3923,27 +3954,27 @@
         <v>78</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>76</v>
+        <v>216</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3966,15 +3997,17 @@
         <v>87</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>220</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>76</v>
@@ -4023,7 +4056,7 @@
         <v>76</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -4038,21 +4071,21 @@
         <v>98</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4078,13 +4111,13 @@
         <v>128</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4134,7 +4167,7 @@
         <v>76</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -4149,25 +4182,25 @@
         <v>98</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4186,16 +4219,16 @@
         <v>87</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4245,7 +4278,7 @@
         <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4254,31 +4287,31 @@
         <v>78</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>98</v>
+        <v>235</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>76</v>
+        <v>237</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4297,15 +4330,17 @@
         <v>87</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>76</v>
@@ -4354,7 +4389,7 @@
         <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -4363,27 +4398,27 @@
         <v>78</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>98</v>
+        <v>235</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>76</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4406,15 +4441,17 @@
         <v>76</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>247</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>76</v>
@@ -4463,7 +4500,7 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4472,10 +4509,10 @@
         <v>78</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>98</v>
+        <v>235</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>76</v>
@@ -4484,15 +4521,15 @@
         <v>76</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>76</v>
+        <v>237</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4515,16 +4552,16 @@
         <v>87</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4550,31 +4587,31 @@
         <v>76</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="Z27" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>86</v>
@@ -4589,10 +4626,10 @@
         <v>98</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>76</v>
@@ -4600,14 +4637,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4626,16 +4663,16 @@
         <v>87</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4661,31 +4698,31 @@
         <v>76</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Y28" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="Z28" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -4694,27 +4731,27 @@
         <v>86</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>76</v>
+        <v>266</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4737,16 +4774,16 @@
         <v>76</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4772,13 +4809,13 @@
         <v>76</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>76</v>
@@ -4796,7 +4833,7 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -4805,7 +4842,7 @@
         <v>78</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>98</v>
@@ -4814,18 +4851,18 @@
         <v>76</v>
       </c>
       <c r="AL29" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>76</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4848,23 +4885,23 @@
         <v>87</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q30" t="s" s="2">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="R30" t="s" s="2">
         <v>76</v>
@@ -4885,13 +4922,13 @@
         <v>76</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>76</v>
@@ -4909,7 +4946,7 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -4927,7 +4964,7 @@
         <v>76</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>76</v>
@@ -4935,10 +4972,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4961,15 +4998,17 @@
         <v>76</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>284</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>285</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>76</v>
@@ -4994,13 +5033,13 @@
         <v>76</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>76</v>
@@ -5018,7 +5057,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -5027,7 +5066,7 @@
         <v>78</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>98</v>
@@ -5039,19 +5078,19 @@
         <v>76</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>76</v>
+        <v>266</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5070,15 +5109,17 @@
         <v>87</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>292</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>76</v>
@@ -5127,7 +5168,7 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -5136,27 +5177,27 @@
         <v>86</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>98</v>
+        <v>235</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>76</v>
+        <v>237</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5179,16 +5220,16 @@
         <v>76</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5214,13 +5255,13 @@
         <v>76</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>76</v>
@@ -5238,7 +5279,7 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5247,7 +5288,7 @@
         <v>86</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>98</v>
@@ -5256,18 +5297,18 @@
         <v>76</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>76</v>
+        <v>266</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5290,16 +5331,16 @@
         <v>76</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5349,7 +5390,7 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -5358,27 +5399,27 @@
         <v>78</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>98</v>
+        <v>235</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>76</v>
+        <v>237</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5401,16 +5442,16 @@
         <v>87</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5460,7 +5501,7 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5469,27 +5510,27 @@
         <v>86</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>98</v>
+        <v>235</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>76</v>
+        <v>237</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5512,13 +5553,13 @@
         <v>76</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5569,7 +5610,7 @@
         <v>76</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5584,10 +5625,10 @@
         <v>98</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>76</v>
@@ -5595,10 +5636,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5621,13 +5662,13 @@
         <v>76</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5678,7 +5719,7 @@
         <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -5693,10 +5734,10 @@
         <v>98</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>76</v>
@@ -5704,10 +5745,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5730,15 +5771,17 @@
         <v>76</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>325</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>76</v>
@@ -5787,7 +5830,7 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -5796,27 +5839,27 @@
         <v>78</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>98</v>
+        <v>235</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>76</v>
+        <v>237</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5922,10 +5965,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6033,10 +6076,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6062,13 +6105,13 @@
         <v>100</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6118,7 +6161,7 @@
         <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6127,7 +6170,7 @@
         <v>86</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>98</v>
@@ -6139,15 +6182,15 @@
         <v>76</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6173,13 +6216,13 @@
         <v>128</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6208,10 +6251,10 @@
         <v>150</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>76</v>
@@ -6229,7 +6272,7 @@
         <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6250,15 +6293,15 @@
         <v>76</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6281,16 +6324,16 @@
         <v>87</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6340,7 +6383,7 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6349,7 +6392,7 @@
         <v>86</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>98</v>
@@ -6361,15 +6404,15 @@
         <v>76</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>341</v>
+        <v>349</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6395,13 +6438,13 @@
         <v>100</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6451,7 +6494,7 @@
         <v>76</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
@@ -6472,15 +6515,15 @@
         <v>76</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6503,15 +6546,17 @@
         <v>76</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>76</v>
@@ -6560,7 +6605,7 @@
         <v>76</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -6569,27 +6614,27 @@
         <v>86</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>98</v>
+        <v>235</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>76</v>
+        <v>237</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6695,10 +6740,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6806,10 +6851,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6835,13 +6880,13 @@
         <v>100</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6891,7 +6936,7 @@
         <v>76</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -6900,7 +6945,7 @@
         <v>86</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>98</v>
@@ -6912,15 +6957,15 @@
         <v>76</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6946,13 +6991,13 @@
         <v>128</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -6981,10 +7026,10 @@
         <v>150</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>76</v>
@@ -7002,7 +7047,7 @@
         <v>76</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7023,15 +7068,15 @@
         <v>76</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7054,16 +7099,16 @@
         <v>87</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7113,7 +7158,7 @@
         <v>76</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -7122,7 +7167,7 @@
         <v>86</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>98</v>
@@ -7134,15 +7179,15 @@
         <v>76</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>341</v>
+        <v>349</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7168,13 +7213,13 @@
         <v>100</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7224,7 +7269,7 @@
         <v>76</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -7245,15 +7290,15 @@
         <v>76</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7276,16 +7321,16 @@
         <v>87</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7311,13 +7356,13 @@
         <v>76</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>76</v>
@@ -7335,7 +7380,7 @@
         <v>76</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -7344,27 +7389,27 @@
         <v>78</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>366</v>
+        <v>374</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7387,15 +7432,17 @@
         <v>87</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>378</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>76</v>
@@ -7444,7 +7491,7 @@
         <v>76</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -7453,27 +7500,27 @@
         <v>78</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>98</v>
+        <v>235</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>372</v>
+        <v>380</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7496,13 +7543,13 @@
         <v>76</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7553,7 +7600,7 @@
         <v>76</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -7562,7 +7609,7 @@
         <v>78</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>98</v>
@@ -7574,15 +7621,15 @@
         <v>76</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>76</v>
+        <v>104</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7688,10 +7735,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7761,16 +7808,16 @@
         <v>76</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="AF56" t="s" s="2">
         <v>114</v>
@@ -7799,14 +7846,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -7828,16 +7875,16 @@
         <v>107</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>110</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>76</v>
@@ -7886,7 +7933,7 @@
         <v>76</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
@@ -7907,15 +7954,15 @@
         <v>76</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7941,10 +7988,10 @@
         <v>100</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7995,7 +8042,7 @@
         <v>76</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>86</v>
@@ -8004,7 +8051,7 @@
         <v>86</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>98</v>
@@ -8016,15 +8063,15 @@
         <v>76</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>76</v>
+        <v>104</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8047,15 +8094,17 @@
         <v>76</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>398</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>76</v>
@@ -8104,7 +8153,7 @@
         <v>76</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
@@ -8113,19 +8162,19 @@
         <v>78</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>76</v>
+        <v>401</v>
       </c>
     </row>
   </sheetData>

--- a/tiflow-core/fhir-error-codes/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Communication-DispReq.xlsx
+++ b/tiflow-core/fhir-error-codes/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Communication-DispReq.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2100" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2091" uniqueCount="392">
   <si>
     <t>Property</t>
   </si>
@@ -496,160 +496,157 @@
     <t>Meta.security</t>
   </si>
   <si>
+    <t>Communication.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>Communication.implicitRules</t>
+  </si>
+  <si>
+    <t>A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+  </si>
+  <si>
+    <t>Resource.implicitRules</t>
+  </si>
+  <si>
+    <t>Communication.language</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
+</t>
+  </si>
+  <si>
+    <t>Language of the resource content</t>
+  </si>
+  <si>
+    <t>The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+  </si>
+  <si>
+    <t>preferred</t>
+  </si>
+  <si>
+    <t>A human language.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+  </si>
+  <si>
+    <t>Resource.language</t>
+  </si>
+  <si>
+    <t>Communication.text</t>
+  </si>
+  <si>
+    <t>narrative
+htmlxhtmldisplay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narrative
+</t>
+  </si>
+  <si>
+    <t>Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+  </si>
+  <si>
+    <t>DomainResource.text</t>
+  </si>
+  <si>
+    <t>Act.text?</t>
+  </si>
+  <si>
+    <t>Communication.contained</t>
+  </si>
+  <si>
+    <t>inline resources
+anonymous resourcescontained resources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resource
+</t>
+  </si>
+  <si>
+    <t>Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+  </si>
+  <si>
+    <t>DomainResource.contained</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Communication.extension</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>Communication.extension:flowType</t>
+  </si>
+  <si>
+    <t>flowType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://gematik.de/fhir/erp/StructureDefinition/GEM_ERP_EX_PrescriptionType}
+</t>
+  </si>
+  <si>
+    <t>Art der Verschreibung</t>
+  </si>
+  <si>
+    <t>Definiert den Typ des Rezepts. Das Codesystem enthält alle unterstützten Formulare.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
-    <t>CV</t>
-  </si>
-  <si>
-    <t>Communication.meta.tag</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
-  </si>
-  <si>
-    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
-  </si>
-  <si>
-    <t>Meta.tag</t>
-  </si>
-  <si>
-    <t>Communication.implicitRules</t>
-  </si>
-  <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
-  </si>
-  <si>
-    <t>Resource.implicitRules</t>
-  </si>
-  <si>
-    <t>Communication.language</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
-  </si>
-  <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>A human language.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
-  </si>
-  <si>
-    <t>Resource.language</t>
-  </si>
-  <si>
-    <t>Communication.text</t>
-  </si>
-  <si>
-    <t>narrative
-htmlxhtmldisplay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narrative
-</t>
-  </si>
-  <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
-  </si>
-  <si>
-    <t>DomainResource.text</t>
-  </si>
-  <si>
-    <t>Act.text?</t>
-  </si>
-  <si>
-    <t>Communication.contained</t>
-  </si>
-  <si>
-    <t>inline resources
-anonymous resourcescontained resources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource
-</t>
-  </si>
-  <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
-  </si>
-  <si>
-    <t>DomainResource.contained</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Communication.extension</t>
-  </si>
-  <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>Communication.extension:flowType</t>
-  </si>
-  <si>
-    <t>flowType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://gematik.de/fhir/erp/StructureDefinition/GEM_ERP_EX_PrescriptionType}
-</t>
-  </si>
-  <si>
-    <t>Art der Verschreibung</t>
-  </si>
-  <si>
-    <t>Definiert den Typ des Rezepts. Das Codesystem enthält alle unterstützten Formulare.</t>
-  </si>
-  <si>
     <t>Communication.modifierExtension</t>
   </si>
   <si>
@@ -691,9 +688,6 @@
     <t>FiveWs.identifier</t>
   </si>
   <si>
-    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
-  </si>
-  <si>
     <t>Communication.instantiatesCanonical</t>
   </si>
   <si>
@@ -707,9 +701,6 @@
     <t>The URL pointing to a FHIR-defined protocol, guideline, orderset or other definition that is adhered to in whole or in part by this Communication.</t>
   </si>
   <si>
-    <t>see [Canonical References](http://hl7.org/fhir/R4/references.html#canonical)</t>
-  </si>
-  <si>
     <t>Event.instantiatesCanonical</t>
   </si>
   <si>
@@ -751,14 +742,7 @@
     <t>This must point to some sort of a 'Request' resource, such as CarePlan, CommunicationRequest, ServiceRequest, MedicationRequest, etc.</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
-  </si>
-  <si>
     <t>Event.basedOn</t>
-  </si>
-  <si>
-    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
   </si>
   <si>
     <t>Communication.partOf</t>
@@ -774,9 +758,6 @@
     <t>Part of this action.</t>
   </si>
   <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
     <t>Event.partOf</t>
   </si>
   <si>
@@ -849,9 +830,6 @@
     <t>Event.statusReason</t>
   </si>
   <si>
-    <t>CD</t>
-  </si>
-  <si>
     <t>Communication.category</t>
   </si>
   <si>
@@ -904,9 +882,6 @@
   </si>
   <si>
     <t>A channel that was used for this communication (e.g. email, fax).</t>
-  </si>
-  <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
   </si>
   <si>
     <t>Codes for communication mediums such as phone, fax, email, in person, etc.</t>
@@ -1266,13 +1241,7 @@
     <t>Additional notes or commentary about the communication by the sender, receiver or other interested parties.</t>
   </si>
   <si>
-    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
-  </si>
-  <si>
     <t>Event.note</t>
-  </si>
-  <si>
-    <t>Act</t>
   </si>
 </sst>
 </file>
@@ -1629,7 +1598,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="43.421875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="123.23828125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="38.5234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2953,7 +2922,7 @@
         <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>98</v>
@@ -2965,15 +2934,15 @@
         <v>76</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>155</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2999,13 +2968,13 @@
         <v>146</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="N13" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>159</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3031,31 +3000,31 @@
         <v>76</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="Z13" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="Y13" t="s" s="2">
+      <c r="AA13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
@@ -3064,7 +3033,7 @@
         <v>78</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>98</v>
@@ -3076,15 +3045,15 @@
         <v>76</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>155</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3110,13 +3079,13 @@
         <v>128</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3166,7 +3135,7 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -3192,10 +3161,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3218,16 +3187,16 @@
         <v>76</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3253,31 +3222,31 @@
         <v>76</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="Z15" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="Y15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -3303,14 +3272,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3329,16 +3298,16 @@
         <v>76</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3388,7 +3357,7 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3409,19 +3378,19 @@
         <v>76</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3440,16 +3409,16 @@
         <v>76</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3499,7 +3468,7 @@
         <v>76</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3520,15 +3489,15 @@
         <v>76</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3554,10 +3523,10 @@
         <v>107</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3608,7 +3577,7 @@
         <v>113</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -3634,13 +3603,13 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>76</v>
@@ -3662,13 +3631,13 @@
         <v>76</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="L19" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>202</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3719,7 +3688,7 @@
         <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -3728,7 +3697,7 @@
         <v>78</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>76</v>
+        <v>201</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>115</v>
@@ -3745,10 +3714,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3774,16 +3743,16 @@
         <v>107</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="N20" t="s" s="2">
         <v>110</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>76</v>
@@ -3820,19 +3789,19 @@
         <v>76</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3853,15 +3822,15 @@
         <v>76</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3884,19 +3853,19 @@
         <v>87</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="N21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>76</v>
@@ -3945,7 +3914,7 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -3954,27 +3923,27 @@
         <v>78</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AL21" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="AL21" t="s" s="2">
-        <v>215</v>
-      </c>
       <c r="AM21" t="s" s="2">
-        <v>216</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3997,17 +3966,15 @@
         <v>87</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="L22" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>221</v>
-      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>76</v>
@@ -4056,7 +4023,7 @@
         <v>76</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -4071,21 +4038,21 @@
         <v>98</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4111,13 +4078,13 @@
         <v>128</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4167,7 +4134,7 @@
         <v>76</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -4182,25 +4149,25 @@
         <v>98</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4219,16 +4186,16 @@
         <v>87</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="N24" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="L24" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4278,7 +4245,7 @@
         <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4287,31 +4254,31 @@
         <v>78</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>235</v>
+        <v>98</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>237</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4330,17 +4297,15 @@
         <v>87</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>76</v>
@@ -4389,7 +4354,7 @@
         <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -4398,27 +4363,27 @@
         <v>78</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>235</v>
+        <v>98</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>237</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4441,17 +4406,15 @@
         <v>76</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>76</v>
@@ -4500,7 +4463,7 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4509,10 +4472,10 @@
         <v>78</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>235</v>
+        <v>98</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>76</v>
@@ -4521,15 +4484,15 @@
         <v>76</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>237</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4552,16 +4515,16 @@
         <v>87</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4587,13 +4550,13 @@
         <v>76</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>76</v>
@@ -4611,7 +4574,7 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>86</v>
@@ -4626,10 +4589,10 @@
         <v>98</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>76</v>
@@ -4637,14 +4600,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4663,16 +4626,16 @@
         <v>87</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4698,13 +4661,13 @@
         <v>76</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>76</v>
@@ -4722,7 +4685,7 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -4731,27 +4694,27 @@
         <v>86</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>266</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4774,16 +4737,16 @@
         <v>76</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4809,13 +4772,13 @@
         <v>76</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>76</v>
@@ -4833,7 +4796,7 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -4842,7 +4805,7 @@
         <v>78</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>98</v>
@@ -4851,18 +4814,18 @@
         <v>76</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>266</v>
+        <v>76</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4885,23 +4848,23 @@
         <v>87</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q30" t="s" s="2">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="R30" t="s" s="2">
         <v>76</v>
@@ -4922,13 +4885,13 @@
         <v>76</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>76</v>
@@ -4946,7 +4909,7 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -4964,7 +4927,7 @@
         <v>76</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>76</v>
@@ -4972,10 +4935,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4998,17 +4961,15 @@
         <v>76</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>285</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>76</v>
@@ -5033,13 +4994,13 @@
         <v>76</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>76</v>
@@ -5057,7 +5018,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -5066,7 +5027,7 @@
         <v>78</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>98</v>
@@ -5078,19 +5039,19 @@
         <v>76</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>266</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5109,17 +5070,15 @@
         <v>87</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>284</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>76</v>
@@ -5168,7 +5127,7 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -5177,27 +5136,27 @@
         <v>86</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>235</v>
+        <v>98</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>237</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5220,16 +5179,16 @@
         <v>76</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5255,13 +5214,13 @@
         <v>76</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>76</v>
@@ -5279,7 +5238,7 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5288,7 +5247,7 @@
         <v>86</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>98</v>
@@ -5297,18 +5256,18 @@
         <v>76</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>266</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5331,16 +5290,16 @@
         <v>76</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5390,7 +5349,7 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -5399,27 +5358,27 @@
         <v>78</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>235</v>
+        <v>98</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>237</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5442,16 +5401,16 @@
         <v>87</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5501,7 +5460,7 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5510,27 +5469,27 @@
         <v>86</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>235</v>
+        <v>98</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>237</v>
+        <v>76</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5553,13 +5512,13 @@
         <v>76</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5610,7 +5569,7 @@
         <v>76</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5625,10 +5584,10 @@
         <v>98</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>76</v>
@@ -5636,10 +5595,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5662,13 +5621,13 @@
         <v>76</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5719,7 +5678,7 @@
         <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -5734,10 +5693,10 @@
         <v>98</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>76</v>
@@ -5745,10 +5704,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5771,17 +5730,15 @@
         <v>76</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>76</v>
@@ -5830,7 +5787,7 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -5839,27 +5796,27 @@
         <v>78</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>235</v>
+        <v>98</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>237</v>
+        <v>76</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5965,10 +5922,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6076,10 +6033,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6105,13 +6062,13 @@
         <v>100</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6161,7 +6118,7 @@
         <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6170,7 +6127,7 @@
         <v>86</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>98</v>
@@ -6182,15 +6139,15 @@
         <v>76</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6216,13 +6173,13 @@
         <v>128</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6251,10 +6208,10 @@
         <v>150</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>76</v>
@@ -6272,7 +6229,7 @@
         <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6293,15 +6250,15 @@
         <v>76</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6324,16 +6281,16 @@
         <v>87</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6383,7 +6340,7 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6392,7 +6349,7 @@
         <v>86</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>98</v>
@@ -6404,15 +6361,15 @@
         <v>76</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>349</v>
+        <v>341</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6438,13 +6395,13 @@
         <v>100</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6494,7 +6451,7 @@
         <v>76</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
@@ -6515,15 +6472,15 @@
         <v>76</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6546,17 +6503,15 @@
         <v>76</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>76</v>
@@ -6605,7 +6560,7 @@
         <v>76</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -6614,27 +6569,27 @@
         <v>86</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>235</v>
+        <v>98</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>237</v>
+        <v>76</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6740,10 +6695,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6851,10 +6806,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6880,13 +6835,13 @@
         <v>100</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6936,7 +6891,7 @@
         <v>76</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -6945,7 +6900,7 @@
         <v>86</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>98</v>
@@ -6957,15 +6912,15 @@
         <v>76</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6991,13 +6946,13 @@
         <v>128</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7026,10 +6981,10 @@
         <v>150</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>76</v>
@@ -7047,7 +7002,7 @@
         <v>76</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7068,15 +7023,15 @@
         <v>76</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7099,16 +7054,16 @@
         <v>87</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7158,7 +7113,7 @@
         <v>76</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -7167,7 +7122,7 @@
         <v>86</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>98</v>
@@ -7179,15 +7134,15 @@
         <v>76</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>349</v>
+        <v>341</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7213,13 +7168,13 @@
         <v>100</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7269,7 +7224,7 @@
         <v>76</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -7290,15 +7245,15 @@
         <v>76</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7321,16 +7276,16 @@
         <v>87</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7356,13 +7311,13 @@
         <v>76</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>76</v>
@@ -7380,7 +7335,7 @@
         <v>76</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -7389,27 +7344,27 @@
         <v>78</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>374</v>
+        <v>366</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7432,17 +7387,15 @@
         <v>87</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>370</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>76</v>
@@ -7491,7 +7444,7 @@
         <v>76</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -7500,27 +7453,27 @@
         <v>78</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>235</v>
+        <v>98</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>380</v>
+        <v>372</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7543,13 +7496,13 @@
         <v>76</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7600,7 +7553,7 @@
         <v>76</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -7609,7 +7562,7 @@
         <v>78</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>98</v>
@@ -7621,15 +7574,15 @@
         <v>76</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>104</v>
+        <v>76</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7735,10 +7688,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7808,16 +7761,16 @@
         <v>76</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="AF56" t="s" s="2">
         <v>114</v>
@@ -7846,14 +7799,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -7875,16 +7828,16 @@
         <v>107</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>110</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>76</v>
@@ -7933,7 +7886,7 @@
         <v>76</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
@@ -7954,15 +7907,15 @@
         <v>76</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7988,10 +7941,10 @@
         <v>100</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8042,7 +7995,7 @@
         <v>76</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>86</v>
@@ -8051,7 +8004,7 @@
         <v>86</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>98</v>
@@ -8063,15 +8016,15 @@
         <v>76</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>104</v>
+        <v>76</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8094,17 +8047,15 @@
         <v>76</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>399</v>
-      </c>
+        <v>390</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>76</v>
@@ -8153,7 +8104,7 @@
         <v>76</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
@@ -8162,19 +8113,19 @@
         <v>78</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>401</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
